--- a/AAPL_financial_facts_with more fields.xlsx
+++ b/AAPL_financial_facts_with more fields.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/albert/repo/jpmorgan/MLCOETSRL2026-question1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0E72111-7E1F-9A4B-8766-84D4B3D934D0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70B06E5B-95D6-AB4B-AD1D-94480DD61278}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="21340" yWindow="1040" windowWidth="19620" windowHeight="25380" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1400" yWindow="880" windowWidth="39720" windowHeight="25700" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="0000320193_financial_facts" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9910" uniqueCount="171">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9912" uniqueCount="173">
   <si>
     <t>Ticker</t>
   </si>
@@ -549,12 +549,18 @@
   <si>
     <t>cash as % of liquidity</t>
   </si>
+  <si>
+    <t>Current liabilities</t>
+  </si>
+  <si>
+    <t>noncurrent liabilities</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="19" x14ac:knownFonts="1">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -695,6 +701,12 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFEBC88D"/>
+      <name val="Menlo"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="33">
@@ -1038,7 +1050,7 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
@@ -1047,6 +1059,8 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="11" fontId="19" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -4379,7 +4393,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Stockholders Equity</a:t>
+              <a:t>Current liabilities</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4436,38 +4450,32 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Equity!$S$2:$S$11</c:f>
+              <c:f>Liabilities!$AL$61:$AL$68</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yy</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>42638</c:v>
+                  <c:v>43373</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>43009</c:v>
+                  <c:v>43737</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>43373</c:v>
+                  <c:v>44101</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>43737</c:v>
+                  <c:v>44465</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>44101</c:v>
+                  <c:v>44829</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>44465</c:v>
+                  <c:v>45200</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>44829</c:v>
+                  <c:v>45564</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>45200</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>45564</c:v>
-                </c:pt>
-                <c:pt idx="9">
                   <c:v>45928</c:v>
                 </c:pt>
               </c:numCache>
@@ -4475,39 +4483,33 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Equity!$T$2:$T$11</c:f>
+              <c:f>Liabilities!$AM$61:$AM$68</c:f>
               <c:numCache>
                 <c:formatCode>General</c:formatCode>
-                <c:ptCount val="10"/>
+                <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>128249000000</c:v>
+                  <c:v>55012000000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>134047000000</c:v>
+                  <c:v>53960000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>107147000000</c:v>
+                  <c:v>56453000000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>90488000000</c:v>
+                  <c:v>63106000000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>65339000000</c:v>
+                  <c:v>81955000000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>63090000000</c:v>
+                  <c:v>74636000000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>50672000000</c:v>
+                  <c:v>99183000000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>62146000000</c:v>
-                </c:pt>
-                <c:pt idx="8">
-                  <c:v>56950000000</c:v>
-                </c:pt>
-                <c:pt idx="9">
-                  <c:v>73733000000</c:v>
+                  <c:v>86716000000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4515,7 +4517,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-EB73-2B4C-92E1-F5D6AC36F39A}"/>
+              <c16:uniqueId val="{00000000-AE32-9844-BE00-C9CABEC63F72}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4528,11 +4530,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="1917349759"/>
-        <c:axId val="2072806799"/>
+        <c:axId val="1581678079"/>
+        <c:axId val="1581976959"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="1917349759"/>
+        <c:axId val="1581678079"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4575,14 +4577,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2072806799"/>
+        <c:crossAx val="1581976959"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="2072806799"/>
+        <c:axId val="1581976959"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4633,7 +4635,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="1917349759"/>
+        <c:crossAx val="1581678079"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -4724,7 +4726,7 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
-              <a:t>Cash equivalent</a:t>
+              <a:t>Noncurrent liabilities</a:t>
             </a:r>
           </a:p>
         </c:rich>
@@ -4781,7 +4783,7 @@
           </c:marker>
           <c:cat>
             <c:numRef>
-              <c:f>Assets!$Y$35:$Y$42</c:f>
+              <c:f>Liabilities!$AL$75:$AL$82</c:f>
               <c:numCache>
                 <c:formatCode>m/d/yy</c:formatCode>
                 <c:ptCount val="8"/>
@@ -4814,33 +4816,33 @@
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Assets!$Z$35:$Z$42</c:f>
+              <c:f>Liabilities!$AM$75:$AM$82</c:f>
               <c:numCache>
-                <c:formatCode>General</c:formatCode>
+                <c:formatCode>0.00E+00</c:formatCode>
                 <c:ptCount val="8"/>
                 <c:pt idx="0">
-                  <c:v>25913000000</c:v>
+                  <c:v>141712000000</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>48844000000</c:v>
+                  <c:v>142310000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>38016000000</c:v>
+                  <c:v>153157000000</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>34940000000</c:v>
+                  <c:v>162431000000</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>23646000000</c:v>
+                  <c:v>148101000000</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>29965000000</c:v>
+                  <c:v>145129000000</c:v>
                 </c:pt>
                 <c:pt idx="6">
-                  <c:v>29943000000</c:v>
+                  <c:v>131638000000</c:v>
                 </c:pt>
                 <c:pt idx="7">
-                  <c:v>35934000000</c:v>
+                  <c:v>119877000000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4848,7 +4850,7 @@
           <c:smooth val="0"/>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-3753-BE4F-A6DE-036FEDDFB234}"/>
+              <c16:uniqueId val="{00000000-1F57-1F4F-88C4-5CD68F695B71}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4861,11 +4863,11 @@
           <c:showBubbleSize val="0"/>
         </c:dLbls>
         <c:smooth val="0"/>
-        <c:axId val="2051518287"/>
-        <c:axId val="2051634351"/>
+        <c:axId val="1462925392"/>
+        <c:axId val="1462826384"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="2051518287"/>
+        <c:axId val="1462925392"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4908,14 +4910,14 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2051634351"/>
+        <c:crossAx val="1462826384"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="months"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="2051634351"/>
+        <c:axId val="1462826384"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -4935,7 +4937,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:numFmt formatCode="0.00E+00" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4966,7 +4968,7 @@
             <a:endParaRPr lang="en-US"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="2051518287"/>
+        <c:crossAx val="1462925392"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -5462,6 +5464,684 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
+              <a:t>Stockholders Equity</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Equity!$S$2:$S$11</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>42638</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43009</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>43373</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>43737</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44101</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>44465</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>44829</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45200</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>45928</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Equity!$T$2:$T$11</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="10"/>
+                <c:pt idx="0">
+                  <c:v>128249000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>134047000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>107147000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>90488000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>65339000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>63090000000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>50672000000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>62146000000</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>56950000000</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>73733000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EB73-2B4C-92E1-F5D6AC36F39A}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="1917349759"/>
+        <c:axId val="2072806799"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="1917349759"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2072806799"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="2072806799"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="1917349759"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>Cash equivalent</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Assets!$Y$35:$Y$42</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>43373</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43737</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44465</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44829</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45928</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Assets!$Z$35:$Z$42</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>25913000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>48844000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>38016000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>34940000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23646000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>29965000000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>29943000000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>35934000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-3753-BE4F-A6DE-036FEDDFB234}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2051518287"/>
+        <c:axId val="2051634351"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="2051518287"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2051634351"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="2051634351"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2051518287"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>Other assets, current</a:t>
             </a:r>
           </a:p>
@@ -5760,7 +6440,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6093,7 +6773,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart22.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6434,7 +7114,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart23.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -6767,7 +7447,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart24.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7100,7 +7780,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart25.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7433,7 +8113,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -7766,7 +8446,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart29.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -8049,672 +8729,6 @@
           </a:p>
         </c:txPr>
         <c:crossAx val="2072206127"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart28.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>Fixed assets</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Assets!$N$67:$N$74</c:f>
-              <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>43373</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>43737</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>44101</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>44465</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>44829</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>45200</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>45564</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>45928</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Assets!$O$67:$O$74</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>41304000000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>37378000000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>36766000000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>39440000000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>42117000000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>43715000000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>45680000000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>49834000000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-7E1C-5B49-97D4-FAC203B73338}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="2052972831"/>
-        <c:axId val="28755840"/>
-      </c:lineChart>
-      <c:dateAx>
-        <c:axId val="2052972831"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="28755840"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="months"/>
-      </c:dateAx>
-      <c:valAx>
-        <c:axId val="28755840"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2052972831"/>
-        <c:crosses val="autoZero"/>
-        <c:crossBetween val="between"/>
-      </c:valAx>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-    </c:plotArea>
-    <c:plotVisOnly val="1"/>
-    <c:dispBlanksAs val="gap"/>
-    <c:extLst>
-      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
-        <c16r3:dataDisplayOptions16>
-          <c16r3:dispNaAsBlank val="1"/>
-        </c16r3:dataDisplayOptions16>
-      </c:ext>
-    </c:extLst>
-    <c:showDLblsOverMax val="0"/>
-  </c:chart>
-  <c:spPr>
-    <a:solidFill>
-      <a:schemeClr val="bg1"/>
-    </a:solidFill>
-    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-      <a:solidFill>
-        <a:schemeClr val="tx1">
-          <a:lumMod val="15000"/>
-          <a:lumOff val="85000"/>
-        </a:schemeClr>
-      </a:solidFill>
-      <a:round/>
-    </a:ln>
-    <a:effectLst/>
-  </c:spPr>
-  <c:txPr>
-    <a:bodyPr/>
-    <a:lstStyle/>
-    <a:p>
-      <a:pPr>
-        <a:defRPr/>
-      </a:pPr>
-      <a:endParaRPr lang="en-US"/>
-    </a:p>
-  </c:txPr>
-  <c:printSettings>
-    <c:headerFooter/>
-    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
-    <c:pageSetup/>
-  </c:printSettings>
-</c:chartSpace>
-</file>
-
-<file path=xl/charts/chart29.xml><?xml version="1.0" encoding="utf-8"?>
-<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
-  <c:date1904 val="0"/>
-  <c:lang val="en-US"/>
-  <c:roundedCorners val="0"/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
-      <c14:style val="102"/>
-    </mc:Choice>
-    <mc:Fallback>
-      <c:style val="2"/>
-    </mc:Fallback>
-  </mc:AlternateContent>
-  <c:chart>
-    <c:title>
-      <c:tx>
-        <c:rich>
-          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:r>
-              <a:rPr lang="en-US"/>
-              <a:t>vendor non-trade receivables (i.e., advance payments to vendors)</a:t>
-            </a:r>
-          </a:p>
-        </c:rich>
-      </c:tx>
-      <c:overlay val="0"/>
-      <c:spPr>
-        <a:noFill/>
-        <a:ln>
-          <a:noFill/>
-        </a:ln>
-        <a:effectLst/>
-      </c:spPr>
-      <c:txPr>
-        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr>
-            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="65000"/>
-                  <a:lumOff val="35000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:latin typeface="+mn-lt"/>
-              <a:ea typeface="+mn-ea"/>
-              <a:cs typeface="+mn-cs"/>
-            </a:defRPr>
-          </a:pPr>
-          <a:endParaRPr lang="en-US"/>
-        </a:p>
-      </c:txPr>
-    </c:title>
-    <c:autoTitleDeleted val="0"/>
-    <c:plotArea>
-      <c:layout/>
-      <c:lineChart>
-        <c:grouping val="standard"/>
-        <c:varyColors val="0"/>
-        <c:ser>
-          <c:idx val="0"/>
-          <c:order val="0"/>
-          <c:spPr>
-            <a:ln w="28575" cap="rnd">
-              <a:solidFill>
-                <a:schemeClr val="accent1"/>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:marker>
-            <c:symbol val="none"/>
-          </c:marker>
-          <c:cat>
-            <c:numRef>
-              <c:f>Assets!$N$20:$N$27</c:f>
-              <c:numCache>
-                <c:formatCode>m/d/yy</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>43373</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>43737</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>44101</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>44465</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>44829</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>45200</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>45564</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>45928</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Assets!$R$20:$R$27</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="8"/>
-                <c:pt idx="0">
-                  <c:v>25809000000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>22878000000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>21325000000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>25228000000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>32748000000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>31477000000</c:v>
-                </c:pt>
-                <c:pt idx="6">
-                  <c:v>32833000000</c:v>
-                </c:pt>
-                <c:pt idx="7">
-                  <c:v>33180000000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:smooth val="0"/>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-240D-6B46-8689-B857E73742EE}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:dLbls>
-          <c:showLegendKey val="0"/>
-          <c:showVal val="0"/>
-          <c:showCatName val="0"/>
-          <c:showSerName val="0"/>
-          <c:showPercent val="0"/>
-          <c:showBubbleSize val="0"/>
-        </c:dLbls>
-        <c:smooth val="0"/>
-        <c:axId val="2008595823"/>
-        <c:axId val="2008510447"/>
-      </c:lineChart>
-      <c:dateAx>
-        <c:axId val="2008595823"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="b"/>
-        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
-        <c:majorTickMark val="out"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-            <a:solidFill>
-              <a:schemeClr val="tx1">
-                <a:lumMod val="15000"/>
-                <a:lumOff val="85000"/>
-              </a:schemeClr>
-            </a:solidFill>
-            <a:round/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2008510447"/>
-        <c:crosses val="autoZero"/>
-        <c:auto val="1"/>
-        <c:lblOffset val="100"/>
-        <c:baseTimeUnit val="months"/>
-      </c:dateAx>
-      <c:valAx>
-        <c:axId val="2008510447"/>
-        <c:scaling>
-          <c:orientation val="minMax"/>
-        </c:scaling>
-        <c:delete val="0"/>
-        <c:axPos val="l"/>
-        <c:majorGridlines>
-          <c:spPr>
-            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
-              <a:solidFill>
-                <a:schemeClr val="tx1">
-                  <a:lumMod val="15000"/>
-                  <a:lumOff val="85000"/>
-                </a:schemeClr>
-              </a:solidFill>
-              <a:round/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-        </c:majorGridlines>
-        <c:numFmt formatCode="General" sourceLinked="1"/>
-        <c:majorTickMark val="none"/>
-        <c:minorTickMark val="none"/>
-        <c:tickLblPos val="nextTo"/>
-        <c:spPr>
-          <a:noFill/>
-          <a:ln>
-            <a:noFill/>
-          </a:ln>
-          <a:effectLst/>
-        </c:spPr>
-        <c:txPr>
-          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
-          <a:lstStyle/>
-          <a:p>
-            <a:pPr>
-              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
-                <a:solidFill>
-                  <a:schemeClr val="tx1">
-                    <a:lumMod val="65000"/>
-                    <a:lumOff val="35000"/>
-                  </a:schemeClr>
-                </a:solidFill>
-                <a:latin typeface="+mn-lt"/>
-                <a:ea typeface="+mn-ea"/>
-                <a:cs typeface="+mn-cs"/>
-              </a:defRPr>
-            </a:pPr>
-            <a:endParaRPr lang="en-US"/>
-          </a:p>
-        </c:txPr>
-        <c:crossAx val="2008595823"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -9112,6 +9126,672 @@
             </a:pPr>
             <a:r>
               <a:rPr lang="en-US"/>
+              <a:t>Fixed assets</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Assets!$N$67:$N$74</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>43373</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43737</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44465</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44829</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45928</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Assets!$O$67:$O$74</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>41304000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>37378000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>36766000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>39440000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>42117000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>43715000000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45680000000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>49834000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-7E1C-5B49-97D4-FAC203B73338}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2052972831"/>
+        <c:axId val="28755840"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="2052972831"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="28755840"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="28755840"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2052972831"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart31.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
+              <a:t>vendor non-trade receivables (i.e., advance payments to vendors)</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent1"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:cat>
+            <c:numRef>
+              <c:f>Assets!$N$20:$N$27</c:f>
+              <c:numCache>
+                <c:formatCode>m/d/yy</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>43373</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>43737</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>44101</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>44465</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>44829</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>45200</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>45564</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>45928</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Assets!$R$20:$R$27</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>25809000000</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>22878000000</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>21325000000</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>25228000000</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>32748000000</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>31477000000</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>32833000000</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>33180000000</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-240D-6B46-8689-B857E73742EE}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:smooth val="0"/>
+        <c:axId val="2008595823"/>
+        <c:axId val="2008510447"/>
+      </c:lineChart>
+      <c:dateAx>
+        <c:axId val="2008595823"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="m/d/yy" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2008510447"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblOffset val="100"/>
+        <c:baseTimeUnit val="months"/>
+      </c:dateAx>
+      <c:valAx>
+        <c:axId val="2008510447"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="2008595823"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart32.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US"/>
               <a:t>other assets, current / total</a:t>
             </a:r>
           </a:p>
@@ -9410,7 +10090,7 @@
 </c:chartSpace>
 </file>
 
-<file path=xl/charts/chart31.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/charts/chart33.xml><?xml version="1.0" encoding="utf-8"?>
 <c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
   <c:date1904 val="0"/>
   <c:lang val="en-US"/>
@@ -13051,6 +13731,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors32.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors33.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/colors4.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -25676,6 +26436,1038 @@
 </file>
 
 <file path=xl/charts/style31.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style32.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+    </cs:spPr>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="phClr"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style33.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="227">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -29923,6 +31715,78 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId11"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>749148</xdr:colOff>
+      <xdr:row>55</xdr:row>
+      <xdr:rowOff>34472</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>286506</xdr:colOff>
+      <xdr:row>68</xdr:row>
+      <xdr:rowOff>124279</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="15" name="Chart 14">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{4DBA4BBF-AED1-FA63-0186-A65AC8D40935}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId12"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>39</xdr:col>
+      <xdr:colOff>517408</xdr:colOff>
+      <xdr:row>72</xdr:row>
+      <xdr:rowOff>15993</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>45</xdr:col>
+      <xdr:colOff>37630</xdr:colOff>
+      <xdr:row>85</xdr:row>
+      <xdr:rowOff>68674</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="16" name="Chart 15">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{C01881DB-F5C7-15E2-1A02-C64C385F156C}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId13"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -73609,35 +75473,35 @@
         <v>169</v>
       </c>
       <c r="C43">
-        <f>SUM(C7:C8)</f>
+        <f t="shared" ref="C43:J43" si="7">SUM(C7:C8)</f>
         <v>66301000000</v>
       </c>
       <c r="D43">
-        <f>SUM(D7:D8)</f>
+        <f t="shared" si="7"/>
         <v>100557000000</v>
       </c>
       <c r="E43">
-        <f>SUM(E7:E8)</f>
+        <f t="shared" si="7"/>
         <v>90943000000</v>
       </c>
       <c r="F43">
-        <f>SUM(F7:F8)</f>
+        <f t="shared" si="7"/>
         <v>62639000000</v>
       </c>
       <c r="G43">
-        <f>SUM(G7:G8)</f>
+        <f t="shared" si="7"/>
         <v>48304000000</v>
       </c>
       <c r="H43">
-        <f>SUM(H7:H8)</f>
+        <f t="shared" si="7"/>
         <v>61555000000</v>
       </c>
       <c r="I43">
-        <f>SUM(I7:I8)</f>
+        <f t="shared" si="7"/>
         <v>65171000000</v>
       </c>
       <c r="J43">
-        <f>SUM(J7:J8)</f>
+        <f t="shared" si="7"/>
         <v>54697000000</v>
       </c>
     </row>
@@ -73650,31 +75514,31 @@
         <v>0.39083875054674894</v>
       </c>
       <c r="D44">
-        <f t="shared" ref="D44:J44" si="7">D7/D43</f>
+        <f t="shared" ref="D44:J44" si="8">D7/D43</f>
         <v>0.48573445906301899</v>
       </c>
       <c r="E44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.41802007851071549</v>
       </c>
       <c r="F44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.55779945401427222</v>
       </c>
       <c r="G44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.48952467704537928</v>
       </c>
       <c r="H44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.48680042238648363</v>
       </c>
       <c r="I44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.45945282410888277</v>
       </c>
       <c r="J44">
-        <f t="shared" si="7"/>
+        <f t="shared" si="8"/>
         <v>0.65696473298352742</v>
       </c>
     </row>
@@ -75330,7 +77194,8 @@
     <col min="32" max="32" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="34" max="34" width="9.6640625" customWidth="1"/>
     <col min="38" max="38" width="11" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.1640625" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="41" max="41" width="11" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -77258,7 +79123,7 @@
         <v>9967000000</v>
       </c>
     </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A49" s="1">
         <v>44829</v>
       </c>
@@ -77278,7 +79143,7 @@
         <v>7979000000</v>
       </c>
     </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A50" s="1">
         <v>45200</v>
       </c>
@@ -77292,7 +79157,7 @@
         <v>95281000000</v>
       </c>
     </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A51" s="1">
         <v>45200</v>
       </c>
@@ -77306,7 +79171,7 @@
         <v>95281000000</v>
       </c>
     </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A52" s="1">
         <v>45200</v>
       </c>
@@ -77320,7 +79185,7 @@
         <v>95281000000</v>
       </c>
     </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A53" s="1">
         <v>45200</v>
       </c>
@@ -77334,7 +79199,7 @@
         <v>95281000000</v>
       </c>
     </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A54" s="1">
         <v>45564</v>
       </c>
@@ -77348,7 +79213,7 @@
         <v>85750000000</v>
       </c>
     </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A55" s="1">
         <v>45564</v>
       </c>
@@ -77362,7 +79227,7 @@
         <v>85750000000</v>
       </c>
     </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A56" s="1">
         <v>45564</v>
       </c>
@@ -77376,7 +79241,7 @@
         <v>85750000000</v>
       </c>
     </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A57" s="1">
         <v>45564</v>
       </c>
@@ -77390,7 +79255,7 @@
         <v>85750000000</v>
       </c>
     </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A58" s="1">
         <v>45928</v>
       </c>
@@ -77404,7 +79269,7 @@
         <v>78328000000</v>
       </c>
     </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A59" s="1">
         <v>45928</v>
       </c>
@@ -77421,7 +79286,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:39" x14ac:dyDescent="0.2">
       <c r="S60" t="s">
         <v>49</v>
       </c>
@@ -77437,8 +79302,11 @@
       <c r="W60" s="1">
         <v>43373</v>
       </c>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AL60" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="61" spans="1:39" x14ac:dyDescent="0.2">
       <c r="S61" t="s">
         <v>49</v>
       </c>
@@ -77454,8 +79322,14 @@
       <c r="W61" s="1">
         <v>43737</v>
       </c>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AL61" s="1">
+        <v>43373</v>
+      </c>
+      <c r="AM61" s="6">
+        <v>55012000000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:39" x14ac:dyDescent="0.2">
       <c r="S62" t="s">
         <v>49</v>
       </c>
@@ -77471,8 +79345,14 @@
       <c r="W62" s="1">
         <v>43737</v>
       </c>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AL62" s="1">
+        <v>43737</v>
+      </c>
+      <c r="AM62" s="6">
+        <v>53960000000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:39" x14ac:dyDescent="0.2">
       <c r="S63" t="s">
         <v>49</v>
       </c>
@@ -77488,8 +79368,14 @@
       <c r="W63" s="1">
         <v>44101</v>
       </c>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.2">
+      <c r="AL63" s="1">
+        <v>44101</v>
+      </c>
+      <c r="AM63" s="6">
+        <v>56453000000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:39" x14ac:dyDescent="0.2">
       <c r="S64" t="s">
         <v>49</v>
       </c>
@@ -77505,8 +79391,14 @@
       <c r="W64" s="1">
         <v>44101</v>
       </c>
-    </row>
-    <row r="65" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL64" s="1">
+        <v>44465</v>
+      </c>
+      <c r="AM64" s="6">
+        <v>63106000000</v>
+      </c>
+    </row>
+    <row r="65" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S65" t="s">
         <v>49</v>
       </c>
@@ -77522,8 +79414,14 @@
       <c r="W65" s="1">
         <v>44465</v>
       </c>
-    </row>
-    <row r="66" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL65" s="1">
+        <v>44829</v>
+      </c>
+      <c r="AM65" s="6">
+        <v>81955000000</v>
+      </c>
+    </row>
+    <row r="66" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S66" t="s">
         <v>49</v>
       </c>
@@ -77539,8 +79437,14 @@
       <c r="W66" s="1">
         <v>44465</v>
       </c>
-    </row>
-    <row r="67" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL66" s="1">
+        <v>45200</v>
+      </c>
+      <c r="AM66" s="6">
+        <v>74636000000</v>
+      </c>
+    </row>
+    <row r="67" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S67" t="s">
         <v>49</v>
       </c>
@@ -77556,8 +79460,14 @@
       <c r="W67" s="1">
         <v>44829</v>
       </c>
-    </row>
-    <row r="68" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL67" s="1">
+        <v>45564</v>
+      </c>
+      <c r="AM67" s="6">
+        <v>99183000000</v>
+      </c>
+    </row>
+    <row r="68" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S68" t="s">
         <v>49</v>
       </c>
@@ -77573,8 +79483,14 @@
       <c r="W68" s="1">
         <v>44829</v>
       </c>
-    </row>
-    <row r="69" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL68" s="1">
+        <v>45928</v>
+      </c>
+      <c r="AM68" s="6">
+        <v>86716000000</v>
+      </c>
+    </row>
+    <row r="69" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S69" t="s">
         <v>49</v>
       </c>
@@ -77591,7 +79507,7 @@
         <v>45200</v>
       </c>
     </row>
-    <row r="70" spans="19:23" x14ac:dyDescent="0.2">
+    <row r="70" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S70" t="s">
         <v>49</v>
       </c>
@@ -77608,7 +79524,7 @@
         <v>45200</v>
       </c>
     </row>
-    <row r="71" spans="19:23" x14ac:dyDescent="0.2">
+    <row r="71" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S71" t="s">
         <v>49</v>
       </c>
@@ -77625,7 +79541,7 @@
         <v>45564</v>
       </c>
     </row>
-    <row r="72" spans="19:23" x14ac:dyDescent="0.2">
+    <row r="72" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S72" t="s">
         <v>49</v>
       </c>
@@ -77642,7 +79558,7 @@
         <v>45564</v>
       </c>
     </row>
-    <row r="73" spans="19:23" x14ac:dyDescent="0.2">
+    <row r="73" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S73" t="s">
         <v>49</v>
       </c>
@@ -77659,63 +79575,118 @@
         <v>45928</v>
       </c>
     </row>
-    <row r="76" spans="19:23" x14ac:dyDescent="0.2">
+    <row r="74" spans="19:39" x14ac:dyDescent="0.2">
+      <c r="AL74" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="75" spans="19:39" x14ac:dyDescent="0.2">
+      <c r="AL75" s="1">
+        <v>43373</v>
+      </c>
+      <c r="AM75" s="7">
+        <v>141712000000</v>
+      </c>
+    </row>
+    <row r="76" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S76" s="1">
         <v>43373</v>
       </c>
       <c r="T76">
         <v>55888000000</v>
       </c>
-    </row>
-    <row r="77" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL76" s="1">
+        <v>43737</v>
+      </c>
+      <c r="AM76" s="7">
+        <v>142310000000</v>
+      </c>
+    </row>
+    <row r="77" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S77" s="1">
         <v>43737</v>
       </c>
       <c r="T77">
         <v>46236000000</v>
       </c>
-    </row>
-    <row r="78" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL77" s="1">
+        <v>44101</v>
+      </c>
+      <c r="AM77" s="7">
+        <v>153157000000</v>
+      </c>
+    </row>
+    <row r="78" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S78" s="1">
         <v>43737</v>
       </c>
       <c r="T78">
         <v>46236000000</v>
       </c>
-    </row>
-    <row r="79" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL78" s="1">
+        <v>44465</v>
+      </c>
+      <c r="AM78" s="7">
+        <v>162431000000</v>
+      </c>
+    </row>
+    <row r="79" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S79" s="1">
         <v>44101</v>
       </c>
       <c r="T79">
         <v>42296000000</v>
       </c>
-    </row>
-    <row r="80" spans="19:23" x14ac:dyDescent="0.2">
+      <c r="AL79" s="1">
+        <v>44829</v>
+      </c>
+      <c r="AM79" s="7">
+        <v>148101000000</v>
+      </c>
+    </row>
+    <row r="80" spans="19:39" x14ac:dyDescent="0.2">
       <c r="S80" s="1">
         <v>44101</v>
       </c>
       <c r="T80">
         <v>42296000000</v>
       </c>
-    </row>
-    <row r="81" spans="10:32" x14ac:dyDescent="0.2">
+      <c r="AL80" s="1">
+        <v>45200</v>
+      </c>
+      <c r="AM80" s="7">
+        <v>145129000000</v>
+      </c>
+    </row>
+    <row r="81" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S81" s="1">
         <v>44465</v>
       </c>
       <c r="T81">
         <v>54763000000</v>
       </c>
-    </row>
-    <row r="82" spans="10:32" x14ac:dyDescent="0.2">
+      <c r="AL81" s="1">
+        <v>45564</v>
+      </c>
+      <c r="AM81" s="7">
+        <v>131638000000</v>
+      </c>
+    </row>
+    <row r="82" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S82" s="1">
         <v>44465</v>
       </c>
       <c r="T82">
         <v>54763000000</v>
       </c>
-    </row>
-    <row r="83" spans="10:32" x14ac:dyDescent="0.2">
+      <c r="AL82" s="1">
+        <v>45928</v>
+      </c>
+      <c r="AM82" s="7">
+        <v>119877000000</v>
+      </c>
+    </row>
+    <row r="83" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S83" s="1">
         <v>44829</v>
       </c>
@@ -77723,7 +79694,7 @@
         <v>64115000000</v>
       </c>
     </row>
-    <row r="84" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S84" s="1">
         <v>44829</v>
       </c>
@@ -77731,7 +79702,7 @@
         <v>64115000000</v>
       </c>
     </row>
-    <row r="85" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="85" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S85" s="1">
         <v>45200</v>
       </c>
@@ -77739,7 +79710,7 @@
         <v>62611000000</v>
       </c>
     </row>
-    <row r="86" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="86" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S86" s="1">
         <v>45200</v>
       </c>
@@ -77747,7 +79718,7 @@
         <v>62611000000</v>
       </c>
     </row>
-    <row r="87" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="87" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S87" s="1">
         <v>45564</v>
       </c>
@@ -77755,7 +79726,7 @@
         <v>68960000000</v>
       </c>
     </row>
-    <row r="88" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="88" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S88" s="1">
         <v>45564</v>
       </c>
@@ -77763,7 +79734,7 @@
         <v>68960000000</v>
       </c>
     </row>
-    <row r="89" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="89" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S89" s="1">
         <v>45928</v>
       </c>
@@ -77771,12 +79742,12 @@
         <v>69860000000</v>
       </c>
     </row>
-    <row r="93" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="93" spans="10:39" x14ac:dyDescent="0.2">
       <c r="J93" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="94" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="94" spans="10:39" x14ac:dyDescent="0.2">
       <c r="S94" t="s">
         <v>51</v>
       </c>
@@ -77808,7 +79779,7 @@
         <v>43373</v>
       </c>
     </row>
-    <row r="95" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="10:39" x14ac:dyDescent="0.2">
       <c r="J95" t="s">
         <v>111</v>
       </c>
@@ -77855,7 +79826,7 @@
         <v>43373</v>
       </c>
     </row>
-    <row r="96" spans="10:32" x14ac:dyDescent="0.2">
+    <row r="96" spans="10:39" x14ac:dyDescent="0.2">
       <c r="J96" t="s">
         <v>111</v>
       </c>
